--- a/SamplePageData/SamplePageData.xlsx
+++ b/SamplePageData/SamplePageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ManojNS\eclipse-workspace\NewFrameWork\SamplePageData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7398971-6331-46FD-A123-FA9657F7328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD0F4F5-05B5-47D8-B73E-1D4C8C8C1915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39C5F90A-E468-4E2D-B081-A7ED185AD0A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>email</t>
   </si>
@@ -70,14 +70,21 @@
   </si>
   <si>
     <t>test@123.com</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>mt.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\3\-\5"/>
+    <numFmt numFmtId="165" formatCode="\3\-\5"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -143,7 +150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,23 +465,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D42B13A-4FD4-4677-8B93-E7089CAFE61B}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45415</v>
       </c>
     </row>
   </sheetData>

--- a/SamplePageData/SamplePageData.xlsx
+++ b/SamplePageData/SamplePageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ManojNS\eclipse-workspace\NewFrameWork\SamplePageData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD0F4F5-05B5-47D8-B73E-1D4C8C8C1915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936AF250-C751-4E55-9DD6-A2BD7CE9A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39C5F90A-E468-4E2D-B081-A7ED185AD0A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>email</t>
   </si>
@@ -76,15 +76,20 @@
   </si>
   <si>
     <t>mt.com</t>
+  </si>
+  <si>
+    <t>3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Functional Testing, Automation Testing, Manual Testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\3\-\5"/>
-    <numFmt numFmtId="165" formatCode="\3\-\5"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -150,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,13 +470,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D42B13A-4FD4-4677-8B93-E7089CAFE61B}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -484,8 +493,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -495,8 +507,11 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6">
-        <v>45415</v>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/SamplePageData/SamplePageData.xlsx
+++ b/SamplePageData/SamplePageData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ManojNS\eclipse-workspace\NewFrameWork\SamplePageData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936AF250-C751-4E55-9DD6-A2BD7CE9A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BB74B1-1107-4AAF-938E-0A2BE808A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39C5F90A-E468-4E2D-B081-A7ED185AD0A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>email</t>
   </si>
@@ -81,7 +81,25 @@
     <t>3-5</t>
   </si>
   <si>
+    <t xml:space="preserve"> Functional Testing, Manual Testing</t>
+  </si>
+  <si>
+    <t>Graduate, Post Graduate, Other</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Functional Testing, Automation Testing, Manual Testing</t>
+  </si>
+  <si>
+    <t>exp checkbox Option</t>
+  </si>
+  <si>
+    <t>exp checkbox count</t>
+  </si>
+  <si>
+    <t>education radiobutton count</t>
+  </si>
+  <si>
+    <t>education radiobutton options</t>
   </si>
 </sst>
 </file>
@@ -470,17 +488,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D42B13A-4FD4-4677-8B93-E7089CAFE61B}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -494,10 +513,25 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -510,8 +544,23 @@
       <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/SamplePageData/SamplePageData.xlsx
+++ b/SamplePageData/SamplePageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ManojNS\eclipse-workspace\NewFrameWork\SamplePageData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BB74B1-1107-4AAF-938E-0A2BE808A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F01F5D-977B-4BB5-818E-E25E7F7A036D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39C5F90A-E468-4E2D-B081-A7ED185AD0A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>email</t>
   </si>
@@ -100,6 +100,36 @@
   </si>
   <si>
     <t>education radiobutton options</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  Test message, please ignore it.  </t>
+  </si>
+  <si>
+    <t>nk@456.com</t>
+  </si>
+  <si>
+    <t>testing.com</t>
+  </si>
+  <si>
+    <t>Automation Testing</t>
+  </si>
+  <si>
+    <t>Post Graduate</t>
+  </si>
+  <si>
+    <t>Comment alert message checking.</t>
+  </si>
+  <si>
+    <t>10+</t>
+  </si>
+  <si>
+    <t>nirmal</t>
   </si>
 </sst>
 </file>
@@ -488,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D42B13A-4FD4-4677-8B93-E7089CAFE61B}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -496,10 +526,10 @@
     <col min="5" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -530,8 +560,11 @@
       <c r="J1" t="s">
         <v>4</v>
       </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -560,7 +593,33 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
